--- a/experiment/ELAN_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/ELAN_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.06</v>
+        <v>23.07</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5363</v>
+        <v>0.5371</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.97</v>
+        <v>26.19</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7517</v>
+        <v>0.7584</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.43</v>
+        <v>25.42</v>
       </c>
       <c r="C4" t="n">
-        <v>0.639</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.34</v>
+        <v>26.29</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5795</v>
+        <v>0.5779</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.61</v>
+        <v>23.64</v>
       </c>
       <c r="C6" t="n">
-        <v>0.735</v>
+        <v>0.7372</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>32.95</v>
       </c>
       <c r="C7" t="n">
-        <v>0.796</v>
+        <v>0.7961</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.31</v>
+        <v>28.37</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8194</v>
+        <v>0.8209</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.91</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9221</v>
+        <v>0.9229000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.52</v>
+        <v>32.61</v>
       </c>
       <c r="C10" t="n">
-        <v>0.865</v>
+        <v>0.8661</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.37</v>
+        <v>27.38</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7503</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.06</v>
+        <v>33.22</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9452</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.2</v>
+        <v>34.25</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8802</v>
+        <v>0.8806</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.66</v>
+        <v>26.77</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9469</v>
+        <v>0.9488</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.34</v>
+        <v>27.43</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7782</v>
+        <v>0.7795</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.62</v>
+        <v>28.68</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.783</v>
       </c>
     </row>
   </sheetData>
